--- a/final_data_pipeline/output/311221longform.xlsx
+++ b/final_data_pipeline/output/311221longform.xlsx
@@ -1107,7 +1107,7 @@
         <v>178</v>
       </c>
       <c r="AA2">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB2">
         <v>8000</v>
@@ -1196,7 +1196,7 @@
         <v>178</v>
       </c>
       <c r="AA3">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB3">
         <v>8000</v>
@@ -1288,7 +1288,7 @@
         <v>178</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB4">
         <v>8000</v>
@@ -1380,7 +1380,7 @@
         <v>178</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB5">
         <v>8000</v>
@@ -1472,7 +1472,7 @@
         <v>178</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB6">
         <v>8000</v>
@@ -1564,7 +1564,7 @@
         <v>178</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB7">
         <v>8000</v>
@@ -1656,7 +1656,7 @@
         <v>178</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB8">
         <v>8000</v>
@@ -1748,7 +1748,7 @@
         <v>178</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB9">
         <v>8000</v>
@@ -1846,7 +1846,7 @@
         <v>178</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB10">
         <v>8000</v>
@@ -1935,7 +1935,7 @@
         <v>178</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB11">
         <v>8000</v>
@@ -2027,7 +2027,7 @@
         <v>178</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB12">
         <v>8000</v>
@@ -2125,7 +2125,7 @@
         <v>178</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB13">
         <v>8000</v>
@@ -2220,7 +2220,7 @@
         <v>178</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB14">
         <v>8000</v>
@@ -2309,7 +2309,7 @@
         <v>178</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB15">
         <v>8000</v>
@@ -2398,7 +2398,7 @@
         <v>178</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB16">
         <v>8000</v>
@@ -2487,7 +2487,7 @@
         <v>178</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB17">
         <v>8000</v>
@@ -2576,7 +2576,7 @@
         <v>178</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB18">
         <v>8000</v>
@@ -2668,7 +2668,7 @@
         <v>178</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB19">
         <v>8000</v>
@@ -2760,7 +2760,7 @@
         <v>178</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB20">
         <v>8000</v>
@@ -2852,7 +2852,7 @@
         <v>178</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB21">
         <v>8000</v>
@@ -2944,7 +2944,7 @@
         <v>178</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB22">
         <v>8000</v>
@@ -3039,7 +3039,7 @@
         <v>178</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB23">
         <v>8000</v>
@@ -3131,7 +3131,7 @@
         <v>178</v>
       </c>
       <c r="AA24">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB24">
         <v>8000</v>
@@ -3229,7 +3229,7 @@
         <v>178</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB25">
         <v>8000</v>
@@ -3318,7 +3318,7 @@
         <v>178</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB26">
         <v>8000</v>
@@ -4321,7 +4321,7 @@
         <v>178</v>
       </c>
       <c r="AA37">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB37">
         <v>8000</v>
@@ -4410,7 +4410,7 @@
         <v>178</v>
       </c>
       <c r="AA38">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB38">
         <v>8000</v>
@@ -4499,7 +4499,7 @@
         <v>178</v>
       </c>
       <c r="AA39">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB39">
         <v>8000</v>
@@ -4591,7 +4591,7 @@
         <v>178</v>
       </c>
       <c r="AA40">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB40">
         <v>8000</v>
@@ -4683,7 +4683,7 @@
         <v>178</v>
       </c>
       <c r="AA41">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB41">
         <v>8000</v>
@@ -4775,7 +4775,7 @@
         <v>178</v>
       </c>
       <c r="AA42">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB42">
         <v>8000</v>
@@ -4867,7 +4867,7 @@
         <v>178</v>
       </c>
       <c r="AA43">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB43">
         <v>8000</v>
@@ -4959,7 +4959,7 @@
         <v>178</v>
       </c>
       <c r="AA44">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB44">
         <v>8000</v>
@@ -5051,7 +5051,7 @@
         <v>178</v>
       </c>
       <c r="AA45">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB45">
         <v>8000</v>
@@ -5143,7 +5143,7 @@
         <v>178</v>
       </c>
       <c r="AA46">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB46">
         <v>8000</v>
@@ -5235,7 +5235,7 @@
         <v>178</v>
       </c>
       <c r="AA47">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB47">
         <v>8000</v>
@@ -5324,7 +5324,7 @@
         <v>178</v>
       </c>
       <c r="AA48">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB48">
         <v>8000</v>
@@ -5413,7 +5413,7 @@
         <v>178</v>
       </c>
       <c r="AA49">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB49">
         <v>8000</v>
@@ -5502,7 +5502,7 @@
         <v>178</v>
       </c>
       <c r="AA50">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB50">
         <v>8000</v>
@@ -5591,7 +5591,7 @@
         <v>178</v>
       </c>
       <c r="AA51">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB51">
         <v>8000</v>
@@ -5680,7 +5680,7 @@
         <v>178</v>
       </c>
       <c r="AA52">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB52">
         <v>8000</v>
@@ -5769,7 +5769,7 @@
         <v>178</v>
       </c>
       <c r="AA53">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB53">
         <v>8000</v>
@@ -5861,7 +5861,7 @@
         <v>178</v>
       </c>
       <c r="AA54">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB54">
         <v>8000</v>
@@ -5953,7 +5953,7 @@
         <v>178</v>
       </c>
       <c r="AA55">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB55">
         <v>8000</v>
@@ -6045,7 +6045,7 @@
         <v>178</v>
       </c>
       <c r="AA56">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB56">
         <v>8000</v>
@@ -6143,7 +6143,7 @@
         <v>178</v>
       </c>
       <c r="AA57">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB57">
         <v>8000</v>
@@ -6241,7 +6241,7 @@
         <v>178</v>
       </c>
       <c r="AA58">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB58">
         <v>8000</v>
@@ -6336,7 +6336,7 @@
         <v>178</v>
       </c>
       <c r="AA59">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB59">
         <v>8000</v>
@@ -6428,7 +6428,7 @@
         <v>178</v>
       </c>
       <c r="AA60">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB60">
         <v>8000</v>
@@ -6520,7 +6520,7 @@
         <v>178</v>
       </c>
       <c r="AA61">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB61">
         <v>8000</v>
@@ -6615,7 +6615,7 @@
         <v>178</v>
       </c>
       <c r="AA62">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB62">
         <v>8000</v>
@@ -6707,7 +6707,7 @@
         <v>178</v>
       </c>
       <c r="AA63">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB63">
         <v>8000</v>
@@ -6799,7 +6799,7 @@
         <v>178</v>
       </c>
       <c r="AA64">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB64">
         <v>8000</v>
@@ -6888,7 +6888,7 @@
         <v>178</v>
       </c>
       <c r="AA65">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB65">
         <v>8000</v>
@@ -6977,7 +6977,7 @@
         <v>178</v>
       </c>
       <c r="AA66">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB66">
         <v>8000</v>
@@ -7066,7 +7066,7 @@
         <v>178</v>
       </c>
       <c r="AA67">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB67">
         <v>8000</v>
@@ -7155,7 +7155,7 @@
         <v>178</v>
       </c>
       <c r="AA68">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB68">
         <v>8000</v>
@@ -7247,7 +7247,7 @@
         <v>178</v>
       </c>
       <c r="AA69">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB69">
         <v>8000</v>
@@ -7339,7 +7339,7 @@
         <v>178</v>
       </c>
       <c r="AA70">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB70">
         <v>8000</v>
@@ -7431,7 +7431,7 @@
         <v>178</v>
       </c>
       <c r="AA71">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB71">
         <v>8000</v>
@@ -7520,7 +7520,7 @@
         <v>178</v>
       </c>
       <c r="AA72">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB72">
         <v>8000</v>
@@ -7612,7 +7612,7 @@
         <v>178</v>
       </c>
       <c r="AA73">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB73">
         <v>8000</v>
@@ -7710,7 +7710,7 @@
         <v>178</v>
       </c>
       <c r="AA74">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB74">
         <v>8000</v>
@@ -7802,7 +7802,7 @@
         <v>178</v>
       </c>
       <c r="AA75">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB75">
         <v>8000</v>
@@ -7900,7 +7900,7 @@
         <v>178</v>
       </c>
       <c r="AA76">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB76">
         <v>8000</v>
@@ -7992,7 +7992,7 @@
         <v>178</v>
       </c>
       <c r="AA77">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB77">
         <v>8000</v>
@@ -8084,7 +8084,7 @@
         <v>178</v>
       </c>
       <c r="AA78">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB78">
         <v>8000</v>
@@ -8182,7 +8182,7 @@
         <v>178</v>
       </c>
       <c r="AA79">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB79">
         <v>8000</v>
@@ -8271,7 +8271,7 @@
         <v>178</v>
       </c>
       <c r="AA80">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB80">
         <v>8000</v>
@@ -8360,7 +8360,7 @@
         <v>178</v>
       </c>
       <c r="AA81">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB81">
         <v>8000</v>
@@ -8452,7 +8452,7 @@
         <v>178</v>
       </c>
       <c r="AA82">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB82">
         <v>8000</v>
@@ -8544,7 +8544,7 @@
         <v>178</v>
       </c>
       <c r="AA83">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB83">
         <v>8000</v>
@@ -8636,7 +8636,7 @@
         <v>178</v>
       </c>
       <c r="AA84">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB84">
         <v>8000</v>
@@ -8728,7 +8728,7 @@
         <v>178</v>
       </c>
       <c r="AA85">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB85">
         <v>8000</v>
@@ -8820,7 +8820,7 @@
         <v>178</v>
       </c>
       <c r="AA86">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB86">
         <v>8000</v>
@@ -8918,7 +8918,7 @@
         <v>178</v>
       </c>
       <c r="AA87">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB87">
         <v>8000</v>
@@ -9013,7 +9013,7 @@
         <v>178</v>
       </c>
       <c r="AA88">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB88">
         <v>8000</v>
@@ -9102,7 +9102,7 @@
         <v>178</v>
       </c>
       <c r="AA89">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB89">
         <v>8000</v>
@@ -9191,7 +9191,7 @@
         <v>178</v>
       </c>
       <c r="AA90">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB90">
         <v>8000</v>
@@ -9280,7 +9280,7 @@
         <v>178</v>
       </c>
       <c r="AA91">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB91">
         <v>8000</v>
@@ -9372,7 +9372,7 @@
         <v>178</v>
       </c>
       <c r="AA92">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB92">
         <v>8000</v>
@@ -9464,7 +9464,7 @@
         <v>178</v>
       </c>
       <c r="AA93">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB93">
         <v>8000</v>
@@ -9556,7 +9556,7 @@
         <v>178</v>
       </c>
       <c r="AA94">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB94">
         <v>8000</v>
@@ -9648,7 +9648,7 @@
         <v>178</v>
       </c>
       <c r="AA95">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB95">
         <v>8000</v>
@@ -9740,7 +9740,7 @@
         <v>178</v>
       </c>
       <c r="AA96">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB96">
         <v>8000</v>
@@ -9832,7 +9832,7 @@
         <v>178</v>
       </c>
       <c r="AA97">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB97">
         <v>8000</v>
@@ -9924,7 +9924,7 @@
         <v>178</v>
       </c>
       <c r="AA98">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB98">
         <v>8000</v>
@@ -10016,7 +10016,7 @@
         <v>178</v>
       </c>
       <c r="AA99">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB99">
         <v>8000</v>
@@ -10108,7 +10108,7 @@
         <v>178</v>
       </c>
       <c r="AA100">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB100">
         <v>8000</v>
@@ -10200,7 +10200,7 @@
         <v>178</v>
       </c>
       <c r="AA101">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB101">
         <v>8000</v>
@@ -10289,7 +10289,7 @@
         <v>178</v>
       </c>
       <c r="AA102">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB102">
         <v>8000</v>
@@ -10381,7 +10381,7 @@
         <v>178</v>
       </c>
       <c r="AA103">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB103">
         <v>8000</v>
@@ -10470,7 +10470,7 @@
         <v>178</v>
       </c>
       <c r="AA104">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB104">
         <v>8000</v>
@@ -10559,7 +10559,7 @@
         <v>178</v>
       </c>
       <c r="AA105">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB105">
         <v>8000</v>
@@ -10648,7 +10648,7 @@
         <v>178</v>
       </c>
       <c r="AA106">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB106">
         <v>8000</v>
@@ -10740,7 +10740,7 @@
         <v>178</v>
       </c>
       <c r="AA107">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB107">
         <v>8000</v>
@@ -10829,7 +10829,7 @@
         <v>178</v>
       </c>
       <c r="AA108">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB108">
         <v>8000</v>
@@ -10918,7 +10918,7 @@
         <v>178</v>
       </c>
       <c r="AA109">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB109">
         <v>8000</v>
@@ -11010,7 +11010,7 @@
         <v>178</v>
       </c>
       <c r="AA110">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB110">
         <v>8000</v>
@@ -11099,7 +11099,7 @@
         <v>178</v>
       </c>
       <c r="AA111">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB111">
         <v>8000</v>
@@ -11191,7 +11191,7 @@
         <v>178</v>
       </c>
       <c r="AA112">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB112">
         <v>8000</v>
@@ -11280,7 +11280,7 @@
         <v>178</v>
       </c>
       <c r="AA113">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB113">
         <v>8000</v>
@@ -11369,7 +11369,7 @@
         <v>178</v>
       </c>
       <c r="AA114">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB114">
         <v>8000</v>
@@ -11458,7 +11458,7 @@
         <v>178</v>
       </c>
       <c r="AA115">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB115">
         <v>8000</v>
@@ -11547,7 +11547,7 @@
         <v>178</v>
       </c>
       <c r="AA116">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB116">
         <v>8000</v>
@@ -11636,7 +11636,7 @@
         <v>178</v>
       </c>
       <c r="AA117">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB117">
         <v>8000</v>
@@ -11725,7 +11725,7 @@
         <v>178</v>
       </c>
       <c r="AA118">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB118">
         <v>8000</v>
@@ -11814,7 +11814,7 @@
         <v>178</v>
       </c>
       <c r="AA119">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB119">
         <v>8000</v>
@@ -11906,7 +11906,7 @@
         <v>178</v>
       </c>
       <c r="AA120">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB120">
         <v>8000</v>
@@ -11998,7 +11998,7 @@
         <v>178</v>
       </c>
       <c r="AA121">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB121">
         <v>8000</v>
@@ -12090,7 +12090,7 @@
         <v>178</v>
       </c>
       <c r="AA122">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB122">
         <v>8000</v>
@@ -12188,7 +12188,7 @@
         <v>178</v>
       </c>
       <c r="AA123">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB123">
         <v>8000</v>
@@ -12286,7 +12286,7 @@
         <v>178</v>
       </c>
       <c r="AA124">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB124">
         <v>8000</v>
@@ -12384,7 +12384,7 @@
         <v>178</v>
       </c>
       <c r="AA125">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB125">
         <v>8000</v>
@@ -12485,7 +12485,7 @@
         <v>178</v>
       </c>
       <c r="AA126">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB126">
         <v>8000</v>
@@ -12580,7 +12580,7 @@
         <v>178</v>
       </c>
       <c r="AA127">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB127">
         <v>8000</v>
@@ -12675,7 +12675,7 @@
         <v>178</v>
       </c>
       <c r="AA128">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB128">
         <v>8000</v>
@@ -12770,7 +12770,7 @@
         <v>178</v>
       </c>
       <c r="AA129">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB129">
         <v>8000</v>
@@ -12862,7 +12862,7 @@
         <v>178</v>
       </c>
       <c r="AA130">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB130">
         <v>8000</v>
@@ -13411,7 +13411,7 @@
         <v>178</v>
       </c>
       <c r="AA136">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB136">
         <v>8000</v>
@@ -13503,7 +13503,7 @@
         <v>178</v>
       </c>
       <c r="AA137">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB137">
         <v>8000</v>
@@ -13601,7 +13601,7 @@
         <v>178</v>
       </c>
       <c r="AA138">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB138">
         <v>8000</v>
@@ -13693,7 +13693,7 @@
         <v>178</v>
       </c>
       <c r="AA139">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB139">
         <v>8000</v>
@@ -13785,7 +13785,7 @@
         <v>178</v>
       </c>
       <c r="AA140">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB140">
         <v>8000</v>
@@ -13877,7 +13877,7 @@
         <v>178</v>
       </c>
       <c r="AA141">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB141">
         <v>8000</v>
@@ -13969,7 +13969,7 @@
         <v>178</v>
       </c>
       <c r="AA142">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB142">
         <v>8000</v>
@@ -14061,7 +14061,7 @@
         <v>178</v>
       </c>
       <c r="AA143">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB143">
         <v>8000</v>
@@ -14153,7 +14153,7 @@
         <v>178</v>
       </c>
       <c r="AA144">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB144">
         <v>8000</v>
@@ -14245,7 +14245,7 @@
         <v>178</v>
       </c>
       <c r="AA145">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB145">
         <v>8000</v>
@@ -14343,7 +14343,7 @@
         <v>178</v>
       </c>
       <c r="AA146">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB146">
         <v>8000</v>
@@ -14441,7 +14441,7 @@
         <v>178</v>
       </c>
       <c r="AA147">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB147">
         <v>8000</v>
@@ -14539,7 +14539,7 @@
         <v>178</v>
       </c>
       <c r="AA148">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB148">
         <v>8000</v>
@@ -14637,7 +14637,7 @@
         <v>178</v>
       </c>
       <c r="AA149">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB149">
         <v>8000</v>
@@ -14735,7 +14735,7 @@
         <v>178</v>
       </c>
       <c r="AA150">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB150">
         <v>8000</v>
@@ -14833,7 +14833,7 @@
         <v>178</v>
       </c>
       <c r="AA151">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB151">
         <v>8000</v>
@@ -14925,7 +14925,7 @@
         <v>178</v>
       </c>
       <c r="AA152">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB152">
         <v>8000</v>
@@ -15014,7 +15014,7 @@
         <v>178</v>
       </c>
       <c r="AA153">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB153">
         <v>8000</v>
@@ -15106,7 +15106,7 @@
         <v>178</v>
       </c>
       <c r="AA154">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB154">
         <v>8000</v>
@@ -15195,7 +15195,7 @@
         <v>178</v>
       </c>
       <c r="AA155">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB155">
         <v>8000</v>
@@ -15284,7 +15284,7 @@
         <v>178</v>
       </c>
       <c r="AA156">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB156">
         <v>8000</v>
@@ -15376,7 +15376,7 @@
         <v>178</v>
       </c>
       <c r="AA157">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB157">
         <v>8000</v>
@@ -15468,7 +15468,7 @@
         <v>178</v>
       </c>
       <c r="AA158">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB158">
         <v>8000</v>
@@ -15560,7 +15560,7 @@
         <v>178</v>
       </c>
       <c r="AA159">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB159">
         <v>8000</v>
@@ -15652,7 +15652,7 @@
         <v>178</v>
       </c>
       <c r="AA160">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB160">
         <v>8000</v>
@@ -15741,7 +15741,7 @@
         <v>178</v>
       </c>
       <c r="AA161">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB161">
         <v>8000</v>
@@ -15830,7 +15830,7 @@
         <v>178</v>
       </c>
       <c r="AA162">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB162">
         <v>8000</v>
@@ -15919,7 +15919,7 @@
         <v>178</v>
       </c>
       <c r="AA163">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB163">
         <v>8000</v>
@@ -16008,7 +16008,7 @@
         <v>178</v>
       </c>
       <c r="AA164">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB164">
         <v>8000</v>
@@ -16097,7 +16097,7 @@
         <v>178</v>
       </c>
       <c r="AA165">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB165">
         <v>8000</v>
@@ -16186,7 +16186,7 @@
         <v>178</v>
       </c>
       <c r="AA166">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB166">
         <v>8000</v>
@@ -16275,7 +16275,7 @@
         <v>178</v>
       </c>
       <c r="AA167">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB167">
         <v>8000</v>
@@ -16364,7 +16364,7 @@
         <v>178</v>
       </c>
       <c r="AA168">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB168">
         <v>8000</v>
@@ -16453,7 +16453,7 @@
         <v>178</v>
       </c>
       <c r="AA169">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB169">
         <v>8000</v>
@@ -16542,7 +16542,7 @@
         <v>178</v>
       </c>
       <c r="AA170">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB170">
         <v>8000</v>
@@ -16631,7 +16631,7 @@
         <v>178</v>
       </c>
       <c r="AA171">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB171">
         <v>8000</v>
@@ -16720,7 +16720,7 @@
         <v>178</v>
       </c>
       <c r="AA172">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB172">
         <v>8000</v>
@@ -16812,7 +16812,7 @@
         <v>178</v>
       </c>
       <c r="AA173">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB173">
         <v>8000</v>
@@ -16910,7 +16910,7 @@
         <v>178</v>
       </c>
       <c r="AA174">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB174">
         <v>8000</v>
@@ -17002,7 +17002,7 @@
         <v>178</v>
       </c>
       <c r="AA175">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB175">
         <v>8000</v>
@@ -17094,7 +17094,7 @@
         <v>178</v>
       </c>
       <c r="AA176">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB176">
         <v>8000</v>
@@ -17186,7 +17186,7 @@
         <v>178</v>
       </c>
       <c r="AA177">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB177">
         <v>8000</v>
@@ -17275,7 +17275,7 @@
         <v>178</v>
       </c>
       <c r="AA178">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB178">
         <v>8000</v>
@@ -17364,7 +17364,7 @@
         <v>178</v>
       </c>
       <c r="AA179">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB179">
         <v>8000</v>
@@ -17456,7 +17456,7 @@
         <v>178</v>
       </c>
       <c r="AA180">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB180">
         <v>8000</v>
@@ -18919,7 +18919,7 @@
         <v>178</v>
       </c>
       <c r="AA196">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB196">
         <v>8000</v>
@@ -19008,7 +19008,7 @@
         <v>178</v>
       </c>
       <c r="AA197">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB197">
         <v>8000</v>
@@ -19097,7 +19097,7 @@
         <v>178</v>
       </c>
       <c r="AA198">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB198">
         <v>8000</v>
@@ -19186,7 +19186,7 @@
         <v>178</v>
       </c>
       <c r="AA199">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB199">
         <v>8000</v>
@@ -19278,7 +19278,7 @@
         <v>178</v>
       </c>
       <c r="AA200">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB200">
         <v>8000</v>
@@ -19376,7 +19376,7 @@
         <v>178</v>
       </c>
       <c r="AA201">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB201">
         <v>8000</v>
@@ -19468,7 +19468,7 @@
         <v>178</v>
       </c>
       <c r="AA202">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB202">
         <v>8000</v>
@@ -19560,7 +19560,7 @@
         <v>178</v>
       </c>
       <c r="AA203">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB203">
         <v>8000</v>
@@ -19652,7 +19652,7 @@
         <v>178</v>
       </c>
       <c r="AA204">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB204">
         <v>8000</v>
@@ -19744,7 +19744,7 @@
         <v>178</v>
       </c>
       <c r="AA205">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB205">
         <v>8000</v>
@@ -19833,7 +19833,7 @@
         <v>178</v>
       </c>
       <c r="AA206">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB206">
         <v>8000</v>
@@ -19922,7 +19922,7 @@
         <v>178</v>
       </c>
       <c r="AA207">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB207">
         <v>8000</v>
@@ -20011,7 +20011,7 @@
         <v>178</v>
       </c>
       <c r="AA208">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB208">
         <v>8000</v>
@@ -20100,7 +20100,7 @@
         <v>178</v>
       </c>
       <c r="AA209">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB209">
         <v>8000</v>
@@ -20192,7 +20192,7 @@
         <v>178</v>
       </c>
       <c r="AA210">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB210">
         <v>8000</v>
@@ -20284,7 +20284,7 @@
         <v>178</v>
       </c>
       <c r="AA211">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB211">
         <v>8000</v>
@@ -20382,7 +20382,7 @@
         <v>178</v>
       </c>
       <c r="AA212">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB212">
         <v>8000</v>
@@ -20480,7 +20480,7 @@
         <v>178</v>
       </c>
       <c r="AA213">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB213">
         <v>8000</v>
@@ -20578,7 +20578,7 @@
         <v>178</v>
       </c>
       <c r="AA214">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB214">
         <v>8000</v>
@@ -20670,7 +20670,7 @@
         <v>178</v>
       </c>
       <c r="AA215">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB215">
         <v>8000</v>
@@ -20759,7 +20759,7 @@
         <v>178</v>
       </c>
       <c r="AA216">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB216">
         <v>8000</v>
@@ -20848,7 +20848,7 @@
         <v>178</v>
       </c>
       <c r="AA217">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB217">
         <v>8000</v>
@@ -20937,7 +20937,7 @@
         <v>178</v>
       </c>
       <c r="AA218">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB218">
         <v>8000</v>
@@ -21026,7 +21026,7 @@
         <v>178</v>
       </c>
       <c r="AA219">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB219">
         <v>8000</v>
@@ -21115,7 +21115,7 @@
         <v>178</v>
       </c>
       <c r="AA220">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB220">
         <v>8000</v>
@@ -21204,7 +21204,7 @@
         <v>178</v>
       </c>
       <c r="AA221">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB221">
         <v>8000</v>
@@ -21293,7 +21293,7 @@
         <v>178</v>
       </c>
       <c r="AA222">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB222">
         <v>8000</v>
@@ -21382,7 +21382,7 @@
         <v>178</v>
       </c>
       <c r="AA223">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB223">
         <v>8000</v>
@@ -21474,7 +21474,7 @@
         <v>178</v>
       </c>
       <c r="AA224">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB224">
         <v>8000</v>
@@ -21566,7 +21566,7 @@
         <v>178</v>
       </c>
       <c r="AA225">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB225">
         <v>8000</v>
@@ -21658,7 +21658,7 @@
         <v>178</v>
       </c>
       <c r="AA226">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB226">
         <v>8000</v>
@@ -21750,7 +21750,7 @@
         <v>178</v>
       </c>
       <c r="AA227">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB227">
         <v>8000</v>
@@ -21842,7 +21842,7 @@
         <v>178</v>
       </c>
       <c r="AA228">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB228">
         <v>8000</v>
@@ -21931,7 +21931,7 @@
         <v>178</v>
       </c>
       <c r="AA229">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB229">
         <v>8000</v>
@@ -22020,7 +22020,7 @@
         <v>178</v>
       </c>
       <c r="AA230">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB230">
         <v>8000</v>
@@ -22109,7 +22109,7 @@
         <v>178</v>
       </c>
       <c r="AA231">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB231">
         <v>8000</v>
@@ -22201,7 +22201,7 @@
         <v>178</v>
       </c>
       <c r="AA232">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB232">
         <v>8000</v>
@@ -22290,7 +22290,7 @@
         <v>178</v>
       </c>
       <c r="AA233">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB233">
         <v>8000</v>
@@ -22382,7 +22382,7 @@
         <v>178</v>
       </c>
       <c r="AA234">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB234">
         <v>8000</v>
@@ -22480,7 +22480,7 @@
         <v>178</v>
       </c>
       <c r="AA235">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB235">
         <v>8000</v>
@@ -22578,7 +22578,7 @@
         <v>178</v>
       </c>
       <c r="AA236">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB236">
         <v>8000</v>
@@ -22676,7 +22676,7 @@
         <v>178</v>
       </c>
       <c r="AA237">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB237">
         <v>8000</v>
@@ -22768,7 +22768,7 @@
         <v>178</v>
       </c>
       <c r="AA238">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB238">
         <v>8000</v>
@@ -22860,7 +22860,7 @@
         <v>178</v>
       </c>
       <c r="AA239">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB239">
         <v>8000</v>
@@ -22952,7 +22952,7 @@
         <v>178</v>
       </c>
       <c r="AA240">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB240">
         <v>8000</v>
@@ -23044,7 +23044,7 @@
         <v>178</v>
       </c>
       <c r="AA241">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB241">
         <v>8000</v>
@@ -23142,7 +23142,7 @@
         <v>178</v>
       </c>
       <c r="AA242">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB242">
         <v>8000</v>
@@ -23234,7 +23234,7 @@
         <v>178</v>
       </c>
       <c r="AA243">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB243">
         <v>8000</v>
@@ -23332,7 +23332,7 @@
         <v>178</v>
       </c>
       <c r="AA244">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB244">
         <v>8000</v>
@@ -23424,7 +23424,7 @@
         <v>178</v>
       </c>
       <c r="AA245">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB245">
         <v>8000</v>
@@ -24436,7 +24436,7 @@
         <v>178</v>
       </c>
       <c r="AA256">
-        <v>10</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="AB256">
         <v>8000</v>
@@ -24534,7 +24534,7 @@
         <v>178</v>
       </c>
       <c r="AA257">
-        <v>10</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="AB257">
         <v>8000</v>
@@ -24623,7 +24623,7 @@
         <v>178</v>
       </c>
       <c r="AA258">
-        <v>10</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="AB258">
         <v>8000</v>
@@ -24712,7 +24712,7 @@
         <v>178</v>
       </c>
       <c r="AA259">
-        <v>10</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="AB259">
         <v>8000</v>
@@ -24804,7 +24804,7 @@
         <v>178</v>
       </c>
       <c r="AA260">
-        <v>10</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="AB260">
         <v>8000</v>
@@ -25816,7 +25816,7 @@
         <v>178</v>
       </c>
       <c r="AA271">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB271">
         <v>8000</v>
@@ -25908,7 +25908,7 @@
         <v>178</v>
       </c>
       <c r="AA272">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB272">
         <v>8000</v>
@@ -26000,7 +26000,7 @@
         <v>178</v>
       </c>
       <c r="AA273">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB273">
         <v>8000</v>
@@ -26089,7 +26089,7 @@
         <v>178</v>
       </c>
       <c r="AA274">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB274">
         <v>8000</v>
@@ -26178,7 +26178,7 @@
         <v>178</v>
       </c>
       <c r="AA275">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB275">
         <v>8000</v>
@@ -26267,7 +26267,7 @@
         <v>178</v>
       </c>
       <c r="AA276">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB276">
         <v>8000</v>
@@ -26356,7 +26356,7 @@
         <v>178</v>
       </c>
       <c r="AA277">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB277">
         <v>8000</v>
@@ -26448,7 +26448,7 @@
         <v>178</v>
       </c>
       <c r="AA278">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB278">
         <v>8000</v>
@@ -26540,7 +26540,7 @@
         <v>178</v>
       </c>
       <c r="AA279">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB279">
         <v>8000</v>
@@ -26629,7 +26629,7 @@
         <v>178</v>
       </c>
       <c r="AA280">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB280">
         <v>8000</v>
@@ -26718,7 +26718,7 @@
         <v>178</v>
       </c>
       <c r="AA281">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB281">
         <v>8000</v>
@@ -26810,7 +26810,7 @@
         <v>178</v>
       </c>
       <c r="AA282">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB282">
         <v>8000</v>
@@ -26899,7 +26899,7 @@
         <v>178</v>
       </c>
       <c r="AA283">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB283">
         <v>8000</v>
@@ -26988,7 +26988,7 @@
         <v>178</v>
       </c>
       <c r="AA284">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB284">
         <v>8000</v>
@@ -27080,7 +27080,7 @@
         <v>178</v>
       </c>
       <c r="AA285">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB285">
         <v>8000</v>
@@ -27172,7 +27172,7 @@
         <v>178</v>
       </c>
       <c r="AA286">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB286">
         <v>8000</v>
@@ -27270,7 +27270,7 @@
         <v>178</v>
       </c>
       <c r="AA287">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB287">
         <v>8000</v>
@@ -27362,7 +27362,7 @@
         <v>178</v>
       </c>
       <c r="AA288">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB288">
         <v>8000</v>
@@ -27454,7 +27454,7 @@
         <v>178</v>
       </c>
       <c r="AA289">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB289">
         <v>8000</v>
@@ -27543,7 +27543,7 @@
         <v>178</v>
       </c>
       <c r="AA290">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB290">
         <v>8000</v>
@@ -27632,7 +27632,7 @@
         <v>178</v>
       </c>
       <c r="AA291">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB291">
         <v>8000</v>
@@ -27724,7 +27724,7 @@
         <v>178</v>
       </c>
       <c r="AA292">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB292">
         <v>8000</v>
@@ -27822,7 +27822,7 @@
         <v>178</v>
       </c>
       <c r="AA293">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB293">
         <v>8000</v>
@@ -27920,7 +27920,7 @@
         <v>178</v>
       </c>
       <c r="AA294">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB294">
         <v>8000</v>
@@ -28018,7 +28018,7 @@
         <v>178</v>
       </c>
       <c r="AA295">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB295">
         <v>8000</v>
@@ -33161,7 +33161,7 @@
         <v>178</v>
       </c>
       <c r="AA351">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB351">
         <v>8000</v>
@@ -33250,7 +33250,7 @@
         <v>178</v>
       </c>
       <c r="AA352">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB352">
         <v>8000</v>
@@ -33339,7 +33339,7 @@
         <v>178</v>
       </c>
       <c r="AA353">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB353">
         <v>8000</v>
@@ -33428,7 +33428,7 @@
         <v>178</v>
       </c>
       <c r="AA354">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB354">
         <v>8000</v>
@@ -33517,7 +33517,7 @@
         <v>178</v>
       </c>
       <c r="AA355">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB355">
         <v>8000</v>
@@ -33606,7 +33606,7 @@
         <v>178</v>
       </c>
       <c r="AA356">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB356">
         <v>8000</v>
@@ -33695,7 +33695,7 @@
         <v>178</v>
       </c>
       <c r="AA357">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB357">
         <v>8000</v>
@@ -33787,7 +33787,7 @@
         <v>178</v>
       </c>
       <c r="AA358">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB358">
         <v>8000</v>
@@ -33885,7 +33885,7 @@
         <v>178</v>
       </c>
       <c r="AA359">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB359">
         <v>8000</v>
@@ -33983,7 +33983,7 @@
         <v>178</v>
       </c>
       <c r="AA360">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB360">
         <v>8000</v>
@@ -34081,7 +34081,7 @@
         <v>178</v>
       </c>
       <c r="AA361">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB361">
         <v>8000</v>
@@ -34179,7 +34179,7 @@
         <v>178</v>
       </c>
       <c r="AA362">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB362">
         <v>8000</v>
@@ -34277,7 +34277,7 @@
         <v>178</v>
       </c>
       <c r="AA363">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB363">
         <v>8000</v>
@@ -34375,7 +34375,7 @@
         <v>178</v>
       </c>
       <c r="AA364">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB364">
         <v>8000</v>
@@ -34473,7 +34473,7 @@
         <v>178</v>
       </c>
       <c r="AA365">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB365">
         <v>8000</v>
@@ -34571,7 +34571,7 @@
         <v>178</v>
       </c>
       <c r="AA366">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB366">
         <v>8000</v>
@@ -34669,7 +34669,7 @@
         <v>178</v>
       </c>
       <c r="AA367">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB367">
         <v>8000</v>
@@ -34758,7 +34758,7 @@
         <v>178</v>
       </c>
       <c r="AA368">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB368">
         <v>8000</v>
@@ -34847,7 +34847,7 @@
         <v>178</v>
       </c>
       <c r="AA369">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB369">
         <v>8000</v>
@@ -34939,7 +34939,7 @@
         <v>178</v>
       </c>
       <c r="AA370">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB370">
         <v>8000</v>
@@ -35031,7 +35031,7 @@
         <v>178</v>
       </c>
       <c r="AA371">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB371">
         <v>8000</v>
@@ -35123,7 +35123,7 @@
         <v>178</v>
       </c>
       <c r="AA372">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB372">
         <v>8000</v>
@@ -35215,7 +35215,7 @@
         <v>178</v>
       </c>
       <c r="AA373">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB373">
         <v>8000</v>
@@ -35307,7 +35307,7 @@
         <v>178</v>
       </c>
       <c r="AA374">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB374">
         <v>8000</v>
@@ -35399,7 +35399,7 @@
         <v>178</v>
       </c>
       <c r="AA375">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB375">
         <v>8000</v>
@@ -35491,7 +35491,7 @@
         <v>178</v>
       </c>
       <c r="AA376">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB376">
         <v>8000</v>
@@ -35583,7 +35583,7 @@
         <v>178</v>
       </c>
       <c r="AA377">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB377">
         <v>8000</v>
@@ -35675,7 +35675,7 @@
         <v>178</v>
       </c>
       <c r="AA378">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB378">
         <v>8000</v>
@@ -35767,7 +35767,7 @@
         <v>178</v>
       </c>
       <c r="AA379">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB379">
         <v>8000</v>
@@ -35859,7 +35859,7 @@
         <v>178</v>
       </c>
       <c r="AA380">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB380">
         <v>8000</v>
@@ -35951,7 +35951,7 @@
         <v>178</v>
       </c>
       <c r="AA381">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB381">
         <v>8000</v>
@@ -36040,7 +36040,7 @@
         <v>178</v>
       </c>
       <c r="AA382">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB382">
         <v>8000</v>
@@ -36129,7 +36129,7 @@
         <v>178</v>
       </c>
       <c r="AA383">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB383">
         <v>8000</v>
@@ -36218,7 +36218,7 @@
         <v>178</v>
       </c>
       <c r="AA384">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB384">
         <v>8000</v>
@@ -36307,7 +36307,7 @@
         <v>178</v>
       </c>
       <c r="AA385">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB385">
         <v>8000</v>
@@ -36396,7 +36396,7 @@
         <v>178</v>
       </c>
       <c r="AA386">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB386">
         <v>8000</v>
@@ -36488,7 +36488,7 @@
         <v>178</v>
       </c>
       <c r="AA387">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB387">
         <v>8000</v>
@@ -36577,7 +36577,7 @@
         <v>178</v>
       </c>
       <c r="AA388">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB388">
         <v>8000</v>
@@ -36669,7 +36669,7 @@
         <v>178</v>
       </c>
       <c r="AA389">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB389">
         <v>8000</v>
@@ -36761,7 +36761,7 @@
         <v>178</v>
       </c>
       <c r="AA390">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB390">
         <v>8000</v>
@@ -36853,7 +36853,7 @@
         <v>178</v>
       </c>
       <c r="AA391">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB391">
         <v>8000</v>
@@ -36945,7 +36945,7 @@
         <v>178</v>
       </c>
       <c r="AA392">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB392">
         <v>8000</v>
@@ -37037,7 +37037,7 @@
         <v>178</v>
       </c>
       <c r="AA393">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB393">
         <v>8000</v>
@@ -37126,7 +37126,7 @@
         <v>178</v>
       </c>
       <c r="AA394">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB394">
         <v>8000</v>
@@ -37218,7 +37218,7 @@
         <v>178</v>
       </c>
       <c r="AA395">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB395">
         <v>8000</v>
@@ -37310,7 +37310,7 @@
         <v>178</v>
       </c>
       <c r="AA396">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB396">
         <v>8000</v>
@@ -37402,7 +37402,7 @@
         <v>178</v>
       </c>
       <c r="AA397">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB397">
         <v>8000</v>
@@ -37491,7 +37491,7 @@
         <v>178</v>
       </c>
       <c r="AA398">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB398">
         <v>8000</v>
@@ -37580,7 +37580,7 @@
         <v>178</v>
       </c>
       <c r="AA399">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB399">
         <v>8000</v>
@@ -37669,7 +37669,7 @@
         <v>178</v>
       </c>
       <c r="AA400">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB400">
         <v>8000</v>
@@ -37761,7 +37761,7 @@
         <v>178</v>
       </c>
       <c r="AA401">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB401">
         <v>8000</v>
@@ -37856,7 +37856,7 @@
         <v>178</v>
       </c>
       <c r="AA402">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB402">
         <v>8000</v>
@@ -37945,7 +37945,7 @@
         <v>178</v>
       </c>
       <c r="AA403">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB403">
         <v>8000</v>
@@ -38037,7 +38037,7 @@
         <v>178</v>
       </c>
       <c r="AA404">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB404">
         <v>8000</v>
@@ -38126,7 +38126,7 @@
         <v>178</v>
       </c>
       <c r="AA405">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB405">
         <v>8000</v>
@@ -38218,7 +38218,7 @@
         <v>178</v>
       </c>
       <c r="AA406">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB406">
         <v>8000</v>
@@ -38316,7 +38316,7 @@
         <v>178</v>
       </c>
       <c r="AA407">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB407">
         <v>8000</v>
@@ -38414,7 +38414,7 @@
         <v>178</v>
       </c>
       <c r="AA408">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB408">
         <v>8000</v>
@@ -38509,7 +38509,7 @@
         <v>178</v>
       </c>
       <c r="AA409">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB409">
         <v>8000</v>
@@ -38598,7 +38598,7 @@
         <v>178</v>
       </c>
       <c r="AA410">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB410">
         <v>8000</v>
@@ -38687,7 +38687,7 @@
         <v>178</v>
       </c>
       <c r="AA411">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB411">
         <v>8000</v>
@@ -38776,7 +38776,7 @@
         <v>178</v>
       </c>
       <c r="AA412">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB412">
         <v>8000</v>
@@ -38865,7 +38865,7 @@
         <v>178</v>
       </c>
       <c r="AA413">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB413">
         <v>8000</v>
@@ -38957,7 +38957,7 @@
         <v>178</v>
       </c>
       <c r="AA414">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB414">
         <v>8000</v>
@@ -39049,7 +39049,7 @@
         <v>178</v>
       </c>
       <c r="AA415">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB415">
         <v>8000</v>
@@ -39138,7 +39138,7 @@
         <v>178</v>
       </c>
       <c r="AA416">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB416">
         <v>8000</v>
@@ -39230,7 +39230,7 @@
         <v>178</v>
       </c>
       <c r="AA417">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB417">
         <v>8000</v>
@@ -39322,7 +39322,7 @@
         <v>178</v>
       </c>
       <c r="AA418">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB418">
         <v>8000</v>
@@ -39414,7 +39414,7 @@
         <v>178</v>
       </c>
       <c r="AA419">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB419">
         <v>8000</v>
@@ -39506,7 +39506,7 @@
         <v>178</v>
       </c>
       <c r="AA420">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB420">
         <v>8000</v>
@@ -39595,7 +39595,7 @@
         <v>178</v>
       </c>
       <c r="AA421">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB421">
         <v>8000</v>
@@ -39684,7 +39684,7 @@
         <v>178</v>
       </c>
       <c r="AA422">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB422">
         <v>8000</v>
@@ -39773,7 +39773,7 @@
         <v>178</v>
       </c>
       <c r="AA423">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB423">
         <v>8000</v>
@@ -39862,7 +39862,7 @@
         <v>178</v>
       </c>
       <c r="AA424">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB424">
         <v>8000</v>
@@ -39954,7 +39954,7 @@
         <v>178</v>
       </c>
       <c r="AA425">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB425">
         <v>8000</v>
@@ -40043,7 +40043,7 @@
         <v>178</v>
       </c>
       <c r="AA426">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB426">
         <v>8000</v>
@@ -40132,7 +40132,7 @@
         <v>178</v>
       </c>
       <c r="AA427">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB427">
         <v>8000</v>
@@ -40224,7 +40224,7 @@
         <v>178</v>
       </c>
       <c r="AA428">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB428">
         <v>8000</v>
@@ -40319,7 +40319,7 @@
         <v>178</v>
       </c>
       <c r="AA429">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB429">
         <v>8000</v>
@@ -40408,7 +40408,7 @@
         <v>178</v>
       </c>
       <c r="AA430">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB430">
         <v>8000</v>
@@ -40500,7 +40500,7 @@
         <v>178</v>
       </c>
       <c r="AA431">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB431">
         <v>8000</v>
@@ -40598,7 +40598,7 @@
         <v>178</v>
       </c>
       <c r="AA432">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB432">
         <v>8000</v>
@@ -40696,7 +40696,7 @@
         <v>178</v>
       </c>
       <c r="AA433">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB433">
         <v>8000</v>
@@ -40788,7 +40788,7 @@
         <v>178</v>
       </c>
       <c r="AA434">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB434">
         <v>8000</v>
@@ -40883,7 +40883,7 @@
         <v>178</v>
       </c>
       <c r="AA435">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB435">
         <v>8000</v>
@@ -40975,7 +40975,7 @@
         <v>178</v>
       </c>
       <c r="AA436">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB436">
         <v>8000</v>
@@ -41073,7 +41073,7 @@
         <v>178</v>
       </c>
       <c r="AA437">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB437">
         <v>8000</v>
@@ -41171,7 +41171,7 @@
         <v>178</v>
       </c>
       <c r="AA438">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB438">
         <v>8000</v>
@@ -41263,7 +41263,7 @@
         <v>178</v>
       </c>
       <c r="AA439">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB439">
         <v>8000</v>
@@ -41355,7 +41355,7 @@
         <v>178</v>
       </c>
       <c r="AA440">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB440">
         <v>8000</v>
@@ -41447,7 +41447,7 @@
         <v>178</v>
       </c>
       <c r="AA441">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB441">
         <v>8000</v>
@@ -41539,7 +41539,7 @@
         <v>178</v>
       </c>
       <c r="AA442">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB442">
         <v>8000</v>
@@ -41631,7 +41631,7 @@
         <v>178</v>
       </c>
       <c r="AA443">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB443">
         <v>8000</v>
@@ -41723,7 +41723,7 @@
         <v>178</v>
       </c>
       <c r="AA444">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB444">
         <v>8000</v>
@@ -41815,7 +41815,7 @@
         <v>178</v>
       </c>
       <c r="AA445">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB445">
         <v>8000</v>
@@ -41907,7 +41907,7 @@
         <v>178</v>
       </c>
       <c r="AA446">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB446">
         <v>8000</v>
@@ -41999,7 +41999,7 @@
         <v>178</v>
       </c>
       <c r="AA447">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB447">
         <v>8000</v>
@@ -42091,7 +42091,7 @@
         <v>178</v>
       </c>
       <c r="AA448">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB448">
         <v>8000</v>
@@ -42183,7 +42183,7 @@
         <v>178</v>
       </c>
       <c r="AA449">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB449">
         <v>8000</v>
@@ -42275,7 +42275,7 @@
         <v>178</v>
       </c>
       <c r="AA450">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB450">
         <v>8000</v>
@@ -42367,7 +42367,7 @@
         <v>178</v>
       </c>
       <c r="AA451">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB451">
         <v>8000</v>
@@ -42456,7 +42456,7 @@
         <v>178</v>
       </c>
       <c r="AA452">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB452">
         <v>8000</v>
@@ -42548,7 +42548,7 @@
         <v>178</v>
       </c>
       <c r="AA453">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB453">
         <v>8000</v>
@@ -42640,7 +42640,7 @@
         <v>178</v>
       </c>
       <c r="AA454">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB454">
         <v>8000</v>
@@ -42732,7 +42732,7 @@
         <v>178</v>
       </c>
       <c r="AA455">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB455">
         <v>8000</v>
@@ -42824,7 +42824,7 @@
         <v>178</v>
       </c>
       <c r="AA456">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB456">
         <v>8000</v>
@@ -42916,7 +42916,7 @@
         <v>178</v>
       </c>
       <c r="AA457">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB457">
         <v>8000</v>
@@ -43011,7 +43011,7 @@
         <v>178</v>
       </c>
       <c r="AA458">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB458">
         <v>8000</v>
@@ -43100,7 +43100,7 @@
         <v>178</v>
       </c>
       <c r="AA459">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB459">
         <v>8000</v>
@@ -43189,7 +43189,7 @@
         <v>178</v>
       </c>
       <c r="AA460">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB460">
         <v>8000</v>
@@ -43278,7 +43278,7 @@
         <v>178</v>
       </c>
       <c r="AA461">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB461">
         <v>8000</v>
@@ -43367,7 +43367,7 @@
         <v>178</v>
       </c>
       <c r="AA462">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB462">
         <v>8000</v>
@@ -43456,7 +43456,7 @@
         <v>178</v>
       </c>
       <c r="AA463">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB463">
         <v>8000</v>
@@ -43545,7 +43545,7 @@
         <v>178</v>
       </c>
       <c r="AA464">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB464">
         <v>8000</v>
@@ -43634,7 +43634,7 @@
         <v>178</v>
       </c>
       <c r="AA465">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB465">
         <v>8000</v>
@@ -43726,7 +43726,7 @@
         <v>178</v>
       </c>
       <c r="AA466">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB466">
         <v>8000</v>
@@ -43818,7 +43818,7 @@
         <v>178</v>
       </c>
       <c r="AA467">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB467">
         <v>8000</v>
@@ -43910,7 +43910,7 @@
         <v>178</v>
       </c>
       <c r="AA468">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB468">
         <v>8000</v>
@@ -44002,7 +44002,7 @@
         <v>178</v>
       </c>
       <c r="AA469">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB469">
         <v>8000</v>
@@ -44094,7 +44094,7 @@
         <v>178</v>
       </c>
       <c r="AA470">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB470">
         <v>8000</v>
@@ -44186,7 +44186,7 @@
         <v>178</v>
       </c>
       <c r="AA471">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB471">
         <v>8000</v>
@@ -44278,7 +44278,7 @@
         <v>178</v>
       </c>
       <c r="AA472">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB472">
         <v>8000</v>
@@ -44373,7 +44373,7 @@
         <v>178</v>
       </c>
       <c r="AA473">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB473">
         <v>8000</v>
@@ -44462,7 +44462,7 @@
         <v>178</v>
       </c>
       <c r="AA474">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB474">
         <v>8000</v>
@@ -44551,7 +44551,7 @@
         <v>178</v>
       </c>
       <c r="AA475">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB475">
         <v>8000</v>
@@ -44640,7 +44640,7 @@
         <v>178</v>
       </c>
       <c r="AA476">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB476">
         <v>8000</v>
@@ -44732,7 +44732,7 @@
         <v>178</v>
       </c>
       <c r="AA477">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB477">
         <v>8000</v>
@@ -44824,7 +44824,7 @@
         <v>178</v>
       </c>
       <c r="AA478">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB478">
         <v>8000</v>
@@ -44922,7 +44922,7 @@
         <v>178</v>
       </c>
       <c r="AA479">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB479">
         <v>8000</v>
@@ -45020,7 +45020,7 @@
         <v>178</v>
       </c>
       <c r="AA480">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB480">
         <v>8000</v>
@@ -45112,7 +45112,7 @@
         <v>178</v>
       </c>
       <c r="AA481">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB481">
         <v>8000</v>
@@ -45210,7 +45210,7 @@
         <v>178</v>
       </c>
       <c r="AA482">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB482">
         <v>8000</v>
@@ -45302,7 +45302,7 @@
         <v>178</v>
       </c>
       <c r="AA483">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB483">
         <v>8000</v>
@@ -45394,7 +45394,7 @@
         <v>178</v>
       </c>
       <c r="AA484">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB484">
         <v>8000</v>
@@ -45486,7 +45486,7 @@
         <v>178</v>
       </c>
       <c r="AA485">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB485">
         <v>8000</v>
@@ -45578,7 +45578,7 @@
         <v>178</v>
       </c>
       <c r="AA486">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB486">
         <v>8000</v>
@@ -45670,7 +45670,7 @@
         <v>178</v>
       </c>
       <c r="AA487">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB487">
         <v>8000</v>
@@ -45762,7 +45762,7 @@
         <v>178</v>
       </c>
       <c r="AA488">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB488">
         <v>8000</v>
@@ -45854,7 +45854,7 @@
         <v>178</v>
       </c>
       <c r="AA489">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB489">
         <v>8000</v>
@@ -45946,7 +45946,7 @@
         <v>178</v>
       </c>
       <c r="AA490">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB490">
         <v>8000</v>
@@ -46038,7 +46038,7 @@
         <v>178</v>
       </c>
       <c r="AA491">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB491">
         <v>8000</v>
@@ -46130,7 +46130,7 @@
         <v>178</v>
       </c>
       <c r="AA492">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB492">
         <v>8000</v>
@@ -46225,7 +46225,7 @@
         <v>178</v>
       </c>
       <c r="AA493">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB493">
         <v>8000</v>
@@ -46314,7 +46314,7 @@
         <v>178</v>
       </c>
       <c r="AA494">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB494">
         <v>8000</v>
@@ -46406,7 +46406,7 @@
         <v>178</v>
       </c>
       <c r="AA495">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB495">
         <v>8000</v>
@@ -46498,7 +46498,7 @@
         <v>178</v>
       </c>
       <c r="AA496">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB496">
         <v>8000</v>
@@ -46590,7 +46590,7 @@
         <v>178</v>
       </c>
       <c r="AA497">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB497">
         <v>8000</v>
@@ -46682,7 +46682,7 @@
         <v>178</v>
       </c>
       <c r="AA498">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB498">
         <v>8000</v>
@@ -46774,7 +46774,7 @@
         <v>178</v>
       </c>
       <c r="AA499">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB499">
         <v>8000</v>
@@ -46866,7 +46866,7 @@
         <v>178</v>
       </c>
       <c r="AA500">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB500">
         <v>8000</v>
@@ -46958,7 +46958,7 @@
         <v>178</v>
       </c>
       <c r="AA501">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB501">
         <v>8000</v>
@@ -47050,7 +47050,7 @@
         <v>178</v>
       </c>
       <c r="AA502">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB502">
         <v>8000</v>
@@ -47142,7 +47142,7 @@
         <v>178</v>
       </c>
       <c r="AA503">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB503">
         <v>8000</v>
@@ -47234,7 +47234,7 @@
         <v>178</v>
       </c>
       <c r="AA504">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB504">
         <v>8000</v>
@@ -47326,7 +47326,7 @@
         <v>178</v>
       </c>
       <c r="AA505">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB505">
         <v>8000</v>
@@ -47418,7 +47418,7 @@
         <v>178</v>
       </c>
       <c r="AA506">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB506">
         <v>8000</v>
@@ -47516,7 +47516,7 @@
         <v>178</v>
       </c>
       <c r="AA507">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB507">
         <v>8000</v>
@@ -47605,7 +47605,7 @@
         <v>178</v>
       </c>
       <c r="AA508">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB508">
         <v>8000</v>
@@ -47694,7 +47694,7 @@
         <v>178</v>
       </c>
       <c r="AA509">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB509">
         <v>8000</v>
@@ -47783,7 +47783,7 @@
         <v>178</v>
       </c>
       <c r="AA510">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB510">
         <v>8000</v>
@@ -47872,7 +47872,7 @@
         <v>178</v>
       </c>
       <c r="AA511">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB511">
         <v>8000</v>
@@ -47961,7 +47961,7 @@
         <v>178</v>
       </c>
       <c r="AA512">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB512">
         <v>8000</v>
@@ -48053,7 +48053,7 @@
         <v>178</v>
       </c>
       <c r="AA513">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB513">
         <v>8000</v>
@@ -48145,7 +48145,7 @@
         <v>178</v>
       </c>
       <c r="AA514">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB514">
         <v>8000</v>
@@ -48237,7 +48237,7 @@
         <v>178</v>
       </c>
       <c r="AA515">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB515">
         <v>8000</v>
@@ -48335,7 +48335,7 @@
         <v>178</v>
       </c>
       <c r="AA516">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB516">
         <v>8000</v>
@@ -48433,7 +48433,7 @@
         <v>178</v>
       </c>
       <c r="AA517">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB517">
         <v>8000</v>
@@ -48522,7 +48522,7 @@
         <v>178</v>
       </c>
       <c r="AA518">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB518">
         <v>8000</v>
@@ -48611,7 +48611,7 @@
         <v>178</v>
       </c>
       <c r="AA519">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB519">
         <v>8000</v>
@@ -48700,7 +48700,7 @@
         <v>178</v>
       </c>
       <c r="AA520">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB520">
         <v>8000</v>
@@ -48792,7 +48792,7 @@
         <v>178</v>
       </c>
       <c r="AA521">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB521">
         <v>8000</v>
@@ -48881,7 +48881,7 @@
         <v>178</v>
       </c>
       <c r="AA522">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB522">
         <v>8000</v>
@@ -48973,7 +48973,7 @@
         <v>178</v>
       </c>
       <c r="AA523">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB523">
         <v>8000</v>
@@ -49065,7 +49065,7 @@
         <v>178</v>
       </c>
       <c r="AA524">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB524">
         <v>8000</v>
@@ -49163,7 +49163,7 @@
         <v>178</v>
       </c>
       <c r="AA525">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB525">
         <v>8000</v>
@@ -49261,7 +49261,7 @@
         <v>178</v>
       </c>
       <c r="AA526">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB526">
         <v>8000</v>
@@ -49353,7 +49353,7 @@
         <v>178</v>
       </c>
       <c r="AA527">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB527">
         <v>8000</v>
@@ -49445,7 +49445,7 @@
         <v>178</v>
       </c>
       <c r="AA528">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB528">
         <v>8000</v>
@@ -49534,7 +49534,7 @@
         <v>178</v>
       </c>
       <c r="AA529">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB529">
         <v>8000</v>
@@ -49623,7 +49623,7 @@
         <v>178</v>
       </c>
       <c r="AA530">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB530">
         <v>8000</v>
@@ -49712,7 +49712,7 @@
         <v>178</v>
       </c>
       <c r="AA531">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB531">
         <v>8000</v>
@@ -49801,7 +49801,7 @@
         <v>178</v>
       </c>
       <c r="AA532">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB532">
         <v>8000</v>
@@ -49890,7 +49890,7 @@
         <v>178</v>
       </c>
       <c r="AA533">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB533">
         <v>8000</v>
@@ -49979,7 +49979,7 @@
         <v>178</v>
       </c>
       <c r="AA534">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB534">
         <v>8000</v>
@@ -50068,7 +50068,7 @@
         <v>178</v>
       </c>
       <c r="AA535">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB535">
         <v>8000</v>
@@ -50157,7 +50157,7 @@
         <v>178</v>
       </c>
       <c r="AA536">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB536">
         <v>8000</v>
@@ -50246,7 +50246,7 @@
         <v>178</v>
       </c>
       <c r="AA537">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB537">
         <v>8000</v>
@@ -50335,7 +50335,7 @@
         <v>178</v>
       </c>
       <c r="AA538">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB538">
         <v>8000</v>
@@ -50424,7 +50424,7 @@
         <v>178</v>
       </c>
       <c r="AA539">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB539">
         <v>8000</v>
@@ -50513,7 +50513,7 @@
         <v>178</v>
       </c>
       <c r="AA540">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB540">
         <v>8000</v>
@@ -50602,7 +50602,7 @@
         <v>178</v>
       </c>
       <c r="AA541">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB541">
         <v>8000</v>
@@ -50691,7 +50691,7 @@
         <v>178</v>
       </c>
       <c r="AA542">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB542">
         <v>8000</v>
@@ -50780,7 +50780,7 @@
         <v>178</v>
       </c>
       <c r="AA543">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB543">
         <v>8000</v>
@@ -50869,7 +50869,7 @@
         <v>178</v>
       </c>
       <c r="AA544">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB544">
         <v>8000</v>
@@ -50958,7 +50958,7 @@
         <v>178</v>
       </c>
       <c r="AA545">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB545">
         <v>8000</v>
@@ -51050,7 +51050,7 @@
         <v>178</v>
       </c>
       <c r="AA546">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB546">
         <v>8000</v>
@@ -51142,7 +51142,7 @@
         <v>178</v>
       </c>
       <c r="AA547">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB547">
         <v>8000</v>
@@ -51234,7 +51234,7 @@
         <v>178</v>
       </c>
       <c r="AA548">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB548">
         <v>8000</v>
@@ -51329,7 +51329,7 @@
         <v>178</v>
       </c>
       <c r="AA549">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB549">
         <v>8000</v>
@@ -51421,7 +51421,7 @@
         <v>178</v>
       </c>
       <c r="AA550">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB550">
         <v>8000</v>
@@ -51510,7 +51510,7 @@
         <v>178</v>
       </c>
       <c r="AA551">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB551">
         <v>8000</v>
@@ -51599,7 +51599,7 @@
         <v>178</v>
       </c>
       <c r="AA552">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB552">
         <v>8000</v>
@@ -51688,7 +51688,7 @@
         <v>178</v>
       </c>
       <c r="AA553">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB553">
         <v>8000</v>
@@ -51780,7 +51780,7 @@
         <v>178</v>
       </c>
       <c r="AA554">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB554">
         <v>8000</v>
@@ -51872,7 +51872,7 @@
         <v>178</v>
       </c>
       <c r="AA555">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB555">
         <v>8000</v>
@@ -51964,7 +51964,7 @@
         <v>178</v>
       </c>
       <c r="AA556">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB556">
         <v>8000</v>
@@ -52056,7 +52056,7 @@
         <v>178</v>
       </c>
       <c r="AA557">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB557">
         <v>8000</v>
@@ -52148,7 +52148,7 @@
         <v>178</v>
       </c>
       <c r="AA558">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB558">
         <v>8000</v>
@@ -52240,7 +52240,7 @@
         <v>178</v>
       </c>
       <c r="AA559">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB559">
         <v>8000</v>
@@ -52338,7 +52338,7 @@
         <v>178</v>
       </c>
       <c r="AA560">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB560">
         <v>8000</v>
@@ -52427,7 +52427,7 @@
         <v>178</v>
       </c>
       <c r="AA561">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB561">
         <v>8000</v>
@@ -52519,7 +52519,7 @@
         <v>178</v>
       </c>
       <c r="AA562">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB562">
         <v>8000</v>
@@ -52614,7 +52614,7 @@
         <v>178</v>
       </c>
       <c r="AA563">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB563">
         <v>8000</v>
@@ -52703,7 +52703,7 @@
         <v>178</v>
       </c>
       <c r="AA564">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB564">
         <v>8000</v>
@@ -52792,7 +52792,7 @@
         <v>178</v>
       </c>
       <c r="AA565">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB565">
         <v>8000</v>
@@ -52884,7 +52884,7 @@
         <v>178</v>
       </c>
       <c r="AA566">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB566">
         <v>8000</v>
@@ -52976,7 +52976,7 @@
         <v>178</v>
       </c>
       <c r="AA567">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB567">
         <v>8000</v>
@@ -53065,7 +53065,7 @@
         <v>178</v>
       </c>
       <c r="AA568">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB568">
         <v>8000</v>
@@ -53157,7 +53157,7 @@
         <v>178</v>
       </c>
       <c r="AA569">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB569">
         <v>8000</v>
@@ -53255,7 +53255,7 @@
         <v>178</v>
       </c>
       <c r="AA570">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB570">
         <v>8000</v>
@@ -53344,7 +53344,7 @@
         <v>178</v>
       </c>
       <c r="AA571">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB571">
         <v>8000</v>
@@ -53436,7 +53436,7 @@
         <v>178</v>
       </c>
       <c r="AA572">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB572">
         <v>8000</v>
@@ -53531,7 +53531,7 @@
         <v>178</v>
       </c>
       <c r="AA573">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB573">
         <v>8000</v>
@@ -53623,7 +53623,7 @@
         <v>178</v>
       </c>
       <c r="AA574">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB574">
         <v>8000</v>
@@ -53712,7 +53712,7 @@
         <v>178</v>
       </c>
       <c r="AA575">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB575">
         <v>8000</v>
@@ -53804,7 +53804,7 @@
         <v>178</v>
       </c>
       <c r="AA576">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB576">
         <v>8000</v>
@@ -53896,7 +53896,7 @@
         <v>178</v>
       </c>
       <c r="AA577">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB577">
         <v>8000</v>
@@ -53994,7 +53994,7 @@
         <v>178</v>
       </c>
       <c r="AA578">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB578">
         <v>8000</v>
@@ -54092,7 +54092,7 @@
         <v>178</v>
       </c>
       <c r="AA579">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB579">
         <v>8000</v>
@@ -54184,7 +54184,7 @@
         <v>178</v>
       </c>
       <c r="AA580">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB580">
         <v>8000</v>
@@ -54273,7 +54273,7 @@
         <v>178</v>
       </c>
       <c r="AA581">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB581">
         <v>8000</v>
@@ -54365,7 +54365,7 @@
         <v>178</v>
       </c>
       <c r="AA582">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB582">
         <v>8000</v>
@@ -54454,7 +54454,7 @@
         <v>178</v>
       </c>
       <c r="AA583">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB583">
         <v>8000</v>
@@ -54543,7 +54543,7 @@
         <v>178</v>
       </c>
       <c r="AA584">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB584">
         <v>8000</v>
@@ -54632,7 +54632,7 @@
         <v>178</v>
       </c>
       <c r="AA585">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB585">
         <v>8000</v>
